--- a/planejamento/Relação de empresas.xlsx
+++ b/planejamento/Relação de empresas.xlsx
@@ -1,45 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\APP\GestorPrefeitura\planejamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6B9B1D5C-7FD2-412D-AB08-9453ED90B4A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78084F97-12F5-431B-8296-C743A08CBC98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{234D7ED5-F5B6-4E3A-81C4-25091EA897DD}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
+    <sheet name="Consolidação" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="108">
   <si>
     <t>cod dominio</t>
   </si>
@@ -50,124 +32,127 @@
     <t>cnpj</t>
   </si>
   <si>
+    <t>31.965.256 DIOGO HYOSHIDA</t>
+  </si>
+  <si>
     <t>31.965.256/0001-67</t>
   </si>
   <si>
+    <t>50.277.429 GABRIELLE AJALA LANGUER</t>
+  </si>
+  <si>
     <t>50.277.429/0001-07</t>
   </si>
   <si>
+    <t>A. DOS SANTOS COMERCIO PRODUTOS ALIMENTICIOS</t>
+  </si>
+  <si>
     <t>14.349.099/0001-46</t>
   </si>
   <si>
+    <t>A. M. T . TECIDOS INTERIORES LTDA.</t>
+  </si>
+  <si>
     <t>01.310.940/0001-40</t>
   </si>
   <si>
+    <t>A.M.T DECORACOES LTDA</t>
+  </si>
+  <si>
     <t>49.827.376/0001-63</t>
   </si>
   <si>
+    <t>AADECOR REPRESENTACOES LTDA</t>
+  </si>
+  <si>
     <t>59.554.569/0001-41</t>
   </si>
   <si>
+    <t>ABRACE CLINICA COMPORTAMENTAL LTDA</t>
+  </si>
+  <si>
     <t>43.253.789/0001-03</t>
   </si>
   <si>
+    <t>ABRAHAO REPRESENTACOES LTDA</t>
+  </si>
+  <si>
     <t>07.096.058/0001-20</t>
   </si>
   <si>
+    <t>ACAI DA BARRA PARATI LTDA</t>
+  </si>
+  <si>
     <t>42.705.577/0001-49</t>
   </si>
   <si>
+    <t>ACRD SERVICOS MEDICOS LTDA</t>
+  </si>
+  <si>
     <t>60.121.215/0001-92</t>
   </si>
   <si>
-    <t>31.965.256 DIOGO HYOSHIDA</t>
-  </si>
-  <si>
-    <t>50.277.429 GABRIELLE AJALA LANGUER</t>
-  </si>
-  <si>
-    <t>A. DOS SANTOS COMERCIO PRODUTOS ALIMENTICIOS</t>
-  </si>
-  <si>
-    <t>A. M. T . TECIDOS INTERIORES LTDA.</t>
-  </si>
-  <si>
-    <t>A.M.T DECORACOES LTDA</t>
-  </si>
-  <si>
-    <t>AADECOR REPRESENTACOES LTDA</t>
-  </si>
-  <si>
-    <t>ABRACE CLINICA COMPORTAMENTAL LTDA</t>
-  </si>
-  <si>
-    <t>ABRAHAO REPRESENTACOES LTDA</t>
-  </si>
-  <si>
-    <t>ACAI DA BARRA PARATI LTDA</t>
-  </si>
-  <si>
-    <t>ACRD SERVICOS MEDICOS LTDA</t>
+    <t>BELLA LIFE STUDIO PILATES LTDA</t>
   </si>
   <si>
     <t>22.370.785/0001-27</t>
   </si>
   <si>
-    <t>26.817.957/0001-1 g</t>
+    <t>BEM ESTAR PRODUTOS MEDICOS LTDA ME</t>
+  </si>
+  <si>
+    <t>26.817.957/0001-16</t>
+  </si>
+  <si>
+    <t>BERGO ELETRICIDADE COMERCIO E SERVICOS LTDA</t>
   </si>
   <si>
     <t>37.564.325/0001-07</t>
   </si>
   <si>
+    <t>BIOMAP CONSULTORIA E ASSESSORIA AMBIENTAL LTDA</t>
+  </si>
+  <si>
     <t>43.228.596/0001-94</t>
   </si>
   <si>
+    <t>BRIATO COMERCIO MEDICO-HOSPITALAR E SERVICOS LTDA</t>
+  </si>
+  <si>
     <t>03.321.370/0001-19</t>
   </si>
   <si>
+    <t>BRUNNO PARANA SOCIEDADE INDIVIDUAL DE ADVOCACIA</t>
+  </si>
+  <si>
     <t>36.187.899/0001-40</t>
   </si>
   <si>
+    <t>BYOPRO FISIOTERAPIA ESPECIALIZADA S/S</t>
+  </si>
+  <si>
     <t>23.624.330/0001-53</t>
   </si>
   <si>
+    <t>CAMILA CIRICO DESIGN E SOFTWARE LTDA</t>
+  </si>
+  <si>
     <t>33.448.530/0001-56</t>
   </si>
   <si>
+    <t>CBMR EMPREENDIMENTOS LTDA</t>
+  </si>
+  <si>
     <t>58.542.497/0001-50</t>
   </si>
   <si>
+    <t>CCAT BABY - COLEGIO ALMIRANTE TAMANDARE LTDA</t>
+  </si>
+  <si>
     <t>48.418.478/0001-62</t>
   </si>
   <si>
-    <t>BELLA LIFE STUDIO PILATES LTDA</t>
-  </si>
-  <si>
-    <t>BEM ESTAR PRODUTOS MEDICOS LTDA ME</t>
-  </si>
-  <si>
-    <t>BERGO ELETRICIDADE COMERCIO E SERVICOS LTDA</t>
-  </si>
-  <si>
-    <t>BIOMAP CONSULTORIA E ASSESSORIA AMBIENTAL LTDA</t>
-  </si>
-  <si>
-    <t>BRIATO COMERCIO MEDICO-HOSPITALAR E SERVICOS LTDA</t>
-  </si>
-  <si>
-    <t>BRUNNO PARANA SOCIEDADE INDIVIDUAL DE ADVOCACIA</t>
-  </si>
-  <si>
-    <t>BYOPRO FISIOTERAPIA ESPECIALIZADA S/S</t>
-  </si>
-  <si>
-    <t>CAMILA CIRICO DESIGN E SOFTWARE LTDA</t>
-  </si>
-  <si>
-    <t>CBMR EMPREENDIMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>CCAT BABY - COLEGIO ALMIRANTE TAMANDARE LTDA</t>
+    <t>ESPACO REINTEGRAR LTDA</t>
   </si>
   <si>
     <t>43.547.035/0001-58</t>
@@ -176,62 +161,212 @@
     <t>43.547.035/0002-39</t>
   </si>
   <si>
+    <t>ESPACO SAUDE LTDA</t>
+  </si>
+  <si>
     <t>15.739.280/0001-21</t>
   </si>
   <si>
+    <t>ESPASSO INTERVENCAO COMPORTAMENTAL - ME</t>
+  </si>
+  <si>
     <t>27.114.563/0001-67</t>
   </si>
   <si>
+    <t>ESPETINHOS FELIX LTDA</t>
+  </si>
+  <si>
     <t>49.634.402/0001-37</t>
   </si>
   <si>
+    <t>ESTILO E DESIGN COMERCIO DE MOVEIS LTDA</t>
+  </si>
+  <si>
     <t>32.872.471/0001-86</t>
   </si>
   <si>
+    <t>ESTRELA SERVICOS RURAIS LTDA</t>
+  </si>
+  <si>
     <t>55.606.593/0001-26</t>
   </si>
   <si>
+    <t>ESTUDIO PANTANAL EM DANCA LTDA</t>
+  </si>
+  <si>
     <t>27.373.692/0001-70</t>
   </si>
   <si>
+    <t>ETIKETAR COMERCIO E SERVICOS LTDA</t>
+  </si>
+  <si>
     <t>1 1.482.509/0001-34</t>
   </si>
   <si>
+    <t>FABIANA FERREIRA MOURA LTDA</t>
+  </si>
+  <si>
     <t>52.231.287/0001-64</t>
   </si>
   <si>
-    <t>ESPACO REINTEGRAR LTDA</t>
-  </si>
-  <si>
-    <t>ESPACO SAUDE LTDA</t>
-  </si>
-  <si>
-    <t>ESPASSO INTERVENCAO COMPORTAMENTAL - ME</t>
-  </si>
-  <si>
-    <t>ESPETINHOS FELIX LTDA</t>
-  </si>
-  <si>
-    <t>ESTILO E DESIGN COMERCIO DE MOVEIS LTDA</t>
-  </si>
-  <si>
-    <t>ESTRELA SERVICOS RURAIS LTDA</t>
-  </si>
-  <si>
-    <t>ESTUDIO PANTANAL EM DANCA LTDA</t>
-  </si>
-  <si>
-    <t>ETIKETAR COMERCIO E SERVICOS LTDA</t>
-  </si>
-  <si>
-    <t>FABIANA FERREIRA MOURA LTDA</t>
+    <t>Mes_Competencia</t>
+  </si>
+  <si>
+    <t>CNPJ</t>
+  </si>
+  <si>
+    <t>Nome</t>
+  </si>
+  <si>
+    <t>Qtd_Notas_Ativas</t>
+  </si>
+  <si>
+    <t>Qtd_Notas_Canceladas</t>
+  </si>
+  <si>
+    <t>Faturamento_Bruto</t>
+  </si>
+  <si>
+    <t>ISS_Proprio</t>
+  </si>
+  <si>
+    <t>ISS_Retido</t>
+  </si>
+  <si>
+    <t>Valor_INSS</t>
+  </si>
+  <si>
+    <t>Valor_IR</t>
+  </si>
+  <si>
+    <t>Valor_COFINS</t>
+  </si>
+  <si>
+    <t>Valor_CSLL</t>
+  </si>
+  <si>
+    <t>Valor_PIS</t>
+  </si>
+  <si>
+    <t>Valor_Liquido</t>
+  </si>
+  <si>
+    <t>Valor_ISS</t>
+  </si>
+  <si>
+    <t>02/2026</t>
+  </si>
+  <si>
+    <t>31965256000167</t>
+  </si>
+  <si>
+    <t>50277429000107</t>
+  </si>
+  <si>
+    <t>14349099000146</t>
+  </si>
+  <si>
+    <t>01310940000140</t>
+  </si>
+  <si>
+    <t>49827376000163</t>
+  </si>
+  <si>
+    <t>59554569000141</t>
+  </si>
+  <si>
+    <t>07096058000120</t>
+  </si>
+  <si>
+    <t>42705577000149</t>
+  </si>
+  <si>
+    <t>60121215000192</t>
+  </si>
+  <si>
+    <t>22370785000127</t>
+  </si>
+  <si>
+    <t>37564325000107</t>
+  </si>
+  <si>
+    <t>43228596000194</t>
+  </si>
+  <si>
+    <t>03321370000119</t>
+  </si>
+  <si>
+    <t>36187899000140</t>
+  </si>
+  <si>
+    <t>23624330000153</t>
+  </si>
+  <si>
+    <t>33448530000156</t>
+  </si>
+  <si>
+    <t>58542497000150</t>
+  </si>
+  <si>
+    <t>48418478000162</t>
+  </si>
+  <si>
+    <t>43547035000158</t>
+  </si>
+  <si>
+    <t>43547035000239</t>
+  </si>
+  <si>
+    <t>15739280000121</t>
+  </si>
+  <si>
+    <t>27114563000167</t>
+  </si>
+  <si>
+    <t>49634402000137</t>
+  </si>
+  <si>
+    <t>32872471000186</t>
+  </si>
+  <si>
+    <t>55606593000126</t>
+  </si>
+  <si>
+    <t>27373692000170</t>
+  </si>
+  <si>
+    <t>11482509000134</t>
+  </si>
+  <si>
+    <t>52231287000164</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>SOMA TOTAL DOS PROCESSADOS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -248,7 +383,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -256,15 +391,39 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Vírgula" xfId="1" builtinId="3"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -595,16 +754,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCD1AF90-958D-4C9A-A655-5BE003808748}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.28515625" customWidth="1"/>
-    <col min="2" max="2" width="52.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.33203125" customWidth="1"/>
+    <col min="2" max="2" width="52.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -615,247 +774,1633 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
+      <c r="C7" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
         <v>15</v>
       </c>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
+      <c r="C8" t="s">
         <v>16</v>
       </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
         <v>17</v>
       </c>
-      <c r="C6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
+      <c r="C9" t="s">
         <v>18</v>
       </c>
-      <c r="C7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
         <v>19</v>
       </c>
-      <c r="C8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
+      <c r="C10" t="s">
         <v>20</v>
       </c>
-      <c r="C9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
         <v>21</v>
       </c>
-      <c r="C10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>22</v>
       </c>
-      <c r="C11" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
         <v>33</v>
       </c>
-      <c r="C12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
+      <c r="C17" t="s">
         <v>34</v>
       </c>
-      <c r="C13" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
         <v>35</v>
       </c>
-      <c r="C14" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
+      <c r="C18" t="s">
         <v>36</v>
       </c>
-      <c r="C15" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
         <v>37</v>
       </c>
-      <c r="C16" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
+      <c r="C19" t="s">
         <v>38</v>
       </c>
-      <c r="C17" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" t="s">
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
         <v>39</v>
       </c>
-      <c r="C18" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
+      <c r="C20" t="s">
         <v>40</v>
       </c>
-      <c r="C19" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" t="s">
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
         <v>41</v>
       </c>
-      <c r="C20" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>42</v>
       </c>
-      <c r="C21" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B23" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B25" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" t="s">
         <v>53</v>
       </c>
-      <c r="C22" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" t="s">
-        <v>53</v>
-      </c>
-      <c r="C23" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24" t="s">
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B28" t="s">
         <v>54</v>
       </c>
-      <c r="C24" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B25" t="s">
+      <c r="C28" t="s">
         <v>55</v>
       </c>
-      <c r="C25" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B26" t="s">
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B29" t="s">
         <v>56</v>
       </c>
-      <c r="C26" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B27" t="s">
+      <c r="C29" t="s">
         <v>57</v>
       </c>
-      <c r="C27" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B28" t="s">
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B30" t="s">
         <v>58</v>
       </c>
-      <c r="C28" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B29" t="s">
+      <c r="C30" t="s">
         <v>59</v>
       </c>
-      <c r="C29" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B30" t="s">
+    </row>
+    <row r="31" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B31" t="s">
         <v>60</v>
       </c>
-      <c r="C30" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>61</v>
-      </c>
-      <c r="C31" t="s">
-        <v>52</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:O30"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9" style="3" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G2" s="3">
+        <v>60</v>
+      </c>
+      <c r="H2" s="3">
+        <v>0</v>
+      </c>
+      <c r="I2" s="3">
+        <v>0</v>
+      </c>
+      <c r="J2" s="3">
+        <v>0</v>
+      </c>
+      <c r="K2" s="3">
+        <v>0</v>
+      </c>
+      <c r="L2" s="3">
+        <v>0</v>
+      </c>
+      <c r="M2" s="3">
+        <v>0</v>
+      </c>
+      <c r="N2" s="3">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0</v>
+      </c>
+      <c r="J3" s="3">
+        <v>0</v>
+      </c>
+      <c r="K3" s="3">
+        <v>0</v>
+      </c>
+      <c r="L3" s="3">
+        <v>0</v>
+      </c>
+      <c r="M3" s="3">
+        <v>0</v>
+      </c>
+      <c r="N3" s="3">
+        <v>0</v>
+      </c>
+      <c r="O3" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3">
+        <v>0</v>
+      </c>
+      <c r="J4" s="3">
+        <v>0</v>
+      </c>
+      <c r="K4" s="3">
+        <v>0</v>
+      </c>
+      <c r="L4" s="3">
+        <v>0</v>
+      </c>
+      <c r="M4" s="3">
+        <v>0</v>
+      </c>
+      <c r="N4" s="3">
+        <v>0</v>
+      </c>
+      <c r="O4" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3">
+        <v>0</v>
+      </c>
+      <c r="K5" s="3">
+        <v>0</v>
+      </c>
+      <c r="L5" s="3">
+        <v>0</v>
+      </c>
+      <c r="M5" s="3">
+        <v>0</v>
+      </c>
+      <c r="N5" s="3">
+        <v>0</v>
+      </c>
+      <c r="O5" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>1896</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3">
+        <v>0</v>
+      </c>
+      <c r="N6" s="3">
+        <v>1896</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>4618.4400000000014</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3">
+        <v>0</v>
+      </c>
+      <c r="K7" s="3">
+        <v>0</v>
+      </c>
+      <c r="L7" s="3">
+        <v>0</v>
+      </c>
+      <c r="M7" s="3">
+        <v>0</v>
+      </c>
+      <c r="N7" s="3">
+        <v>4618.4400000000014</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>19945.580000000002</v>
+      </c>
+      <c r="G8" s="3">
+        <v>997.26999999999987</v>
+      </c>
+      <c r="H8" s="3">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3">
+        <v>298.70999999999998</v>
+      </c>
+      <c r="K8" s="3">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3">
+        <v>19646.87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3">
+        <v>0</v>
+      </c>
+      <c r="K9" s="3">
+        <v>0</v>
+      </c>
+      <c r="L9" s="3">
+        <v>0</v>
+      </c>
+      <c r="M9" s="3">
+        <v>0</v>
+      </c>
+      <c r="N9" s="3">
+        <v>0</v>
+      </c>
+      <c r="O9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>77</v>
+      </c>
+      <c r="B10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>2070</v>
+      </c>
+      <c r="G10" s="3">
+        <v>44.91</v>
+      </c>
+      <c r="H10" s="3">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3">
+        <v>0</v>
+      </c>
+      <c r="M10" s="3">
+        <v>0</v>
+      </c>
+      <c r="N10" s="3">
+        <v>2025.09</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>2700</v>
+      </c>
+      <c r="G11" s="3">
+        <v>54.27</v>
+      </c>
+      <c r="H11" s="3">
+        <v>0</v>
+      </c>
+      <c r="I11" s="3">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3">
+        <v>0</v>
+      </c>
+      <c r="K11" s="3">
+        <v>0</v>
+      </c>
+      <c r="L11" s="3">
+        <v>0</v>
+      </c>
+      <c r="M11" s="3">
+        <v>0</v>
+      </c>
+      <c r="N11" s="3">
+        <v>2645.73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" t="s">
+        <v>88</v>
+      </c>
+      <c r="C12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12">
+        <v>4</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>32376.29</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3">
+        <v>0</v>
+      </c>
+      <c r="I12" s="3">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3">
+        <v>0</v>
+      </c>
+      <c r="K12" s="3">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3">
+        <v>0</v>
+      </c>
+      <c r="M12" s="3">
+        <v>0</v>
+      </c>
+      <c r="N12" s="3">
+        <v>32376.29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B13" t="s">
+        <v>89</v>
+      </c>
+      <c r="C13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>400</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="3">
+        <v>0</v>
+      </c>
+      <c r="I13" s="3">
+        <v>0</v>
+      </c>
+      <c r="J13" s="3">
+        <v>0</v>
+      </c>
+      <c r="K13" s="3">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>77</v>
+      </c>
+      <c r="B14" t="s">
+        <v>90</v>
+      </c>
+      <c r="C14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14">
+        <v>15</v>
+      </c>
+      <c r="E14">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
+        <v>48703.66</v>
+      </c>
+      <c r="G14" s="3">
+        <v>182.48</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
+        <v>48521.18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>77</v>
+      </c>
+      <c r="B15" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16">
+        <v>73</v>
+      </c>
+      <c r="E16">
+        <v>4</v>
+      </c>
+      <c r="F16" s="3">
+        <v>107545</v>
+      </c>
+      <c r="G16" s="3">
+        <v>239.5</v>
+      </c>
+      <c r="H16" s="3">
+        <v>0</v>
+      </c>
+      <c r="I16" s="3">
+        <v>0</v>
+      </c>
+      <c r="J16" s="3">
+        <v>0</v>
+      </c>
+      <c r="K16" s="3">
+        <v>0</v>
+      </c>
+      <c r="L16" s="3">
+        <v>0</v>
+      </c>
+      <c r="M16" s="3">
+        <v>0</v>
+      </c>
+      <c r="N16" s="3">
+        <v>107305.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17" t="s">
+        <v>93</v>
+      </c>
+      <c r="C17" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="3">
+        <v>0</v>
+      </c>
+      <c r="I17" s="3">
+        <v>0</v>
+      </c>
+      <c r="J17" s="3">
+        <v>0</v>
+      </c>
+      <c r="K17" s="3">
+        <v>0</v>
+      </c>
+      <c r="L17" s="3">
+        <v>0</v>
+      </c>
+      <c r="M17" s="3">
+        <v>0</v>
+      </c>
+      <c r="N17" s="3">
+        <v>0</v>
+      </c>
+      <c r="O17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>77</v>
+      </c>
+      <c r="B18" t="s">
+        <v>94</v>
+      </c>
+      <c r="C18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3">
+        <v>0</v>
+      </c>
+      <c r="K18" s="3">
+        <v>0</v>
+      </c>
+      <c r="L18" s="3">
+        <v>0</v>
+      </c>
+      <c r="M18" s="3">
+        <v>0</v>
+      </c>
+      <c r="N18" s="3">
+        <v>0</v>
+      </c>
+      <c r="O18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>77</v>
+      </c>
+      <c r="B19" t="s">
+        <v>95</v>
+      </c>
+      <c r="C19" t="s">
+        <v>41</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19" s="3">
+        <v>0</v>
+      </c>
+      <c r="G19" s="3">
+        <v>0</v>
+      </c>
+      <c r="H19" s="3">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3">
+        <v>0</v>
+      </c>
+      <c r="J19" s="3">
+        <v>0</v>
+      </c>
+      <c r="K19" s="3">
+        <v>0</v>
+      </c>
+      <c r="L19" s="3">
+        <v>0</v>
+      </c>
+      <c r="M19" s="3">
+        <v>0</v>
+      </c>
+      <c r="N19" s="3">
+        <v>0</v>
+      </c>
+      <c r="O19" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>77</v>
+      </c>
+      <c r="B20" t="s">
+        <v>96</v>
+      </c>
+      <c r="C20" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20">
+        <v>25</v>
+      </c>
+      <c r="E20">
+        <v>4</v>
+      </c>
+      <c r="F20" s="3">
+        <v>427338.13</v>
+      </c>
+      <c r="G20" s="3">
+        <v>21366.880000000001</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
+        <v>5267.38</v>
+      </c>
+      <c r="K20" s="3">
+        <v>10554.28</v>
+      </c>
+      <c r="L20" s="3">
+        <v>3518.08</v>
+      </c>
+      <c r="M20" s="3">
+        <v>2286.7399999999998</v>
+      </c>
+      <c r="N20" s="3">
+        <v>387351.36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>77</v>
+      </c>
+      <c r="B21" t="s">
+        <v>97</v>
+      </c>
+      <c r="C21" t="s">
+        <v>43</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3">
+        <v>0</v>
+      </c>
+      <c r="M21" s="3">
+        <v>0</v>
+      </c>
+      <c r="N21" s="3">
+        <v>0</v>
+      </c>
+      <c r="O21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>77</v>
+      </c>
+      <c r="B22" t="s">
+        <v>98</v>
+      </c>
+      <c r="C22" t="s">
+        <v>46</v>
+      </c>
+      <c r="D22">
+        <v>89</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
+        <v>380435.81</v>
+      </c>
+      <c r="G22" s="3">
+        <v>19021.75</v>
+      </c>
+      <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
+        <v>5484.86</v>
+      </c>
+      <c r="K22" s="3">
+        <v>11317.94</v>
+      </c>
+      <c r="L22" s="3">
+        <v>3772.62</v>
+      </c>
+      <c r="M22" s="3">
+        <v>2452.1799999999998</v>
+      </c>
+      <c r="N22" s="3">
+        <v>350634.36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>77</v>
+      </c>
+      <c r="B23" t="s">
+        <v>99</v>
+      </c>
+      <c r="C23" t="s">
+        <v>48</v>
+      </c>
+      <c r="D23">
+        <v>23</v>
+      </c>
+      <c r="E23">
+        <v>7</v>
+      </c>
+      <c r="F23" s="3">
+        <v>336174.21</v>
+      </c>
+      <c r="G23" s="3">
+        <v>16808.66</v>
+      </c>
+      <c r="H23" s="3">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3">
+        <v>0</v>
+      </c>
+      <c r="K23" s="3">
+        <v>0</v>
+      </c>
+      <c r="L23" s="3">
+        <v>0</v>
+      </c>
+      <c r="M23" s="3">
+        <v>0</v>
+      </c>
+      <c r="N23" s="3">
+        <v>322970.07</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>77</v>
+      </c>
+      <c r="B24" t="s">
+        <v>100</v>
+      </c>
+      <c r="C24" t="s">
+        <v>50</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>77</v>
+      </c>
+      <c r="B25" t="s">
+        <v>101</v>
+      </c>
+      <c r="C25" t="s">
+        <v>52</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25" s="3">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3">
+        <v>0</v>
+      </c>
+      <c r="H25" s="3">
+        <v>0</v>
+      </c>
+      <c r="I25" s="3">
+        <v>0</v>
+      </c>
+      <c r="J25" s="3">
+        <v>0</v>
+      </c>
+      <c r="K25" s="3">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>77</v>
+      </c>
+      <c r="B26" t="s">
+        <v>102</v>
+      </c>
+      <c r="C26" t="s">
+        <v>54</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3">
+        <v>0</v>
+      </c>
+      <c r="K26" s="3">
+        <v>0</v>
+      </c>
+      <c r="L26" s="3">
+        <v>0</v>
+      </c>
+      <c r="M26" s="3">
+        <v>0</v>
+      </c>
+      <c r="N26" s="3">
+        <v>0</v>
+      </c>
+      <c r="O26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>77</v>
+      </c>
+      <c r="B27" t="s">
+        <v>103</v>
+      </c>
+      <c r="C27" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27">
+        <v>97</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="F27" s="3">
+        <v>24630.25</v>
+      </c>
+      <c r="G27" s="3">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3">
+        <v>371.39</v>
+      </c>
+      <c r="J27" s="3">
+        <v>278.55</v>
+      </c>
+      <c r="K27" s="3">
+        <v>557.31999999999994</v>
+      </c>
+      <c r="L27" s="3">
+        <v>371.39</v>
+      </c>
+      <c r="M27" s="3">
+        <v>120.32</v>
+      </c>
+      <c r="N27" s="3">
+        <v>22931.279999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>77</v>
+      </c>
+      <c r="B28" t="s">
+        <v>104</v>
+      </c>
+      <c r="C28" t="s">
+        <v>58</v>
+      </c>
+      <c r="D28">
+        <v>12</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="F28" s="3">
+        <v>8154.4</v>
+      </c>
+      <c r="G28" s="3">
+        <v>49.24</v>
+      </c>
+      <c r="H28" s="3">
+        <v>0</v>
+      </c>
+      <c r="I28" s="3">
+        <v>0</v>
+      </c>
+      <c r="J28" s="3">
+        <v>0</v>
+      </c>
+      <c r="K28" s="3">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3">
+        <v>8105.16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>77</v>
+      </c>
+      <c r="B29" t="s">
+        <v>105</v>
+      </c>
+      <c r="C29" t="s">
+        <v>60</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>17425</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
+        <v>17425</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>77</v>
+      </c>
+      <c r="B30" t="s">
+        <v>106</v>
+      </c>
+      <c r="C30" t="s">
+        <v>107</v>
+      </c>
+      <c r="D30">
+        <v>351</v>
+      </c>
+      <c r="E30">
+        <v>21</v>
+      </c>
+      <c r="F30" s="3">
+        <v>1415612.77</v>
+      </c>
+      <c r="G30" s="3">
+        <v>58824.959999999992</v>
+      </c>
+      <c r="H30" s="3">
+        <v>0</v>
+      </c>
+      <c r="I30" s="3">
+        <v>371.39</v>
+      </c>
+      <c r="J30" s="3">
+        <v>11329.5</v>
+      </c>
+      <c r="K30" s="3">
+        <v>22429.54</v>
+      </c>
+      <c r="L30" s="3">
+        <v>7662.0900000000011</v>
+      </c>
+      <c r="M30" s="3">
+        <v>4859.24</v>
+      </c>
+      <c r="N30" s="3">
+        <v>1329992.33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>